--- a/research/traditional_assets/database/data/croatia/croatia_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_auto_parts.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0112</v>
+        <v>-0.0644</v>
+      </c>
+      <c r="E2">
+        <v>-0.29</v>
       </c>
       <c r="G2">
-        <v>0.1231002527379949</v>
+        <v>-0.02787926926131851</v>
       </c>
       <c r="H2">
-        <v>0.122156697556866</v>
+        <v>-0.04861000794281176</v>
       </c>
       <c r="I2">
-        <v>-0.08129738837405223</v>
+        <v>-0.0443208895949166</v>
       </c>
       <c r="J2">
-        <v>-0.08129738837405223</v>
+        <v>-0.0443208895949166</v>
       </c>
       <c r="K2">
-        <v>-10.1</v>
+        <v>2.26</v>
       </c>
       <c r="L2">
-        <v>-0.08508845829823083</v>
+        <v>0.01795075456711676</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +627,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="V2">
-        <v>0.08491379310344828</v>
+        <v>0.05476190476190476</v>
       </c>
       <c r="W2">
-        <v>-0.07878315132605304</v>
+        <v>0.02092592592592592</v>
       </c>
       <c r="X2">
-        <v>0.2522973659961613</v>
+        <v>0.1845576756046501</v>
       </c>
       <c r="Y2">
-        <v>-0.3310805173222143</v>
+        <v>-0.1636317496787242</v>
       </c>
       <c r="Z2">
-        <v>0.6776274476223099</v>
+        <v>0.8581555449526276</v>
       </c>
       <c r="AA2">
-        <v>-0.05508934178226866</v>
+        <v>-0.03803421716311089</v>
       </c>
       <c r="AB2">
-        <v>0.1565822680085706</v>
+        <v>0.1285640225471444</v>
       </c>
       <c r="AC2">
-        <v>-0.2116716097908393</v>
+        <v>-0.1665982397102553</v>
       </c>
       <c r="AD2">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="AG2">
-        <v>41.06</v>
+        <v>47.05</v>
       </c>
       <c r="AH2">
-        <v>0.4923413566739606</v>
+        <v>0.4449339207048458</v>
       </c>
       <c r="AI2">
-        <v>0.2941176470588235</v>
+        <v>0.3245501285347044</v>
       </c>
       <c r="AJ2">
-        <v>0.4694717585181797</v>
+        <v>0.4275329395729214</v>
       </c>
       <c r="AK2">
-        <v>0.2754595464913458</v>
+        <v>0.3092343082484391</v>
       </c>
       <c r="AL2">
-        <v>0.523</v>
+        <v>0.761</v>
       </c>
       <c r="AM2">
-        <v>0.375</v>
+        <v>0.629</v>
       </c>
       <c r="AN2">
-        <v>-50.44843049327354</v>
+        <v>26.57894736842105</v>
       </c>
       <c r="AO2">
-        <v>-18.45124282982792</v>
+        <v>-7.332457293035479</v>
       </c>
       <c r="AP2">
-        <v>-46.03139013452915</v>
+        <v>24.76315789473684</v>
       </c>
       <c r="AQ2">
-        <v>-25.73333333333333</v>
+        <v>-8.871224165341813</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +719,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0112</v>
+        <v>-0.0644</v>
+      </c>
+      <c r="E3">
+        <v>-0.29</v>
       </c>
       <c r="G3">
-        <v>0.1231002527379949</v>
+        <v>-0.02787926926131851</v>
       </c>
       <c r="H3">
-        <v>0.122156697556866</v>
+        <v>-0.04861000794281176</v>
       </c>
       <c r="I3">
-        <v>-0.08129738837405223</v>
+        <v>-0.0443208895949166</v>
       </c>
       <c r="J3">
-        <v>-0.08129738837405223</v>
+        <v>-0.0443208895949166</v>
       </c>
       <c r="K3">
-        <v>-10.1</v>
+        <v>2.26</v>
       </c>
       <c r="L3">
-        <v>-0.08508845829823083</v>
+        <v>0.01795075456711676</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +758,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="V3">
-        <v>0.08491379310344828</v>
+        <v>0.05476190476190476</v>
       </c>
       <c r="W3">
-        <v>-0.07878315132605304</v>
+        <v>0.02092592592592592</v>
       </c>
       <c r="X3">
-        <v>0.2522973659961613</v>
+        <v>0.1845576756046501</v>
       </c>
       <c r="Y3">
-        <v>-0.3310805173222143</v>
+        <v>-0.1636317496787242</v>
       </c>
       <c r="Z3">
-        <v>0.6776274476223099</v>
+        <v>0.8581555449526276</v>
       </c>
       <c r="AA3">
-        <v>-0.05508934178226866</v>
+        <v>-0.03803421716311089</v>
       </c>
       <c r="AB3">
-        <v>0.1565822680085706</v>
+        <v>0.1285640225471444</v>
       </c>
       <c r="AC3">
-        <v>-0.2116716097908393</v>
+        <v>-0.1665982397102553</v>
       </c>
       <c r="AD3">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="AG3">
-        <v>41.06</v>
+        <v>47.05</v>
       </c>
       <c r="AH3">
-        <v>0.4923413566739606</v>
+        <v>0.4449339207048458</v>
       </c>
       <c r="AI3">
-        <v>0.2941176470588235</v>
+        <v>0.3245501285347044</v>
       </c>
       <c r="AJ3">
-        <v>0.4694717585181797</v>
+        <v>0.4275329395729214</v>
       </c>
       <c r="AK3">
-        <v>0.2754595464913458</v>
+        <v>0.3092343082484391</v>
       </c>
       <c r="AL3">
-        <v>0.523</v>
+        <v>0.761</v>
       </c>
       <c r="AM3">
-        <v>0.375</v>
+        <v>0.629</v>
       </c>
       <c r="AN3">
-        <v>-50.44843049327354</v>
+        <v>26.57894736842105</v>
       </c>
       <c r="AO3">
-        <v>-18.45124282982792</v>
+        <v>-7.332457293035479</v>
       </c>
       <c r="AP3">
-        <v>-46.03139013452915</v>
+        <v>24.76315789473684</v>
       </c>
       <c r="AQ3">
-        <v>-25.73333333333333</v>
+        <v>-8.871224165341813</v>
       </c>
     </row>
   </sheetData>
